--- a/docs/descomplica_combo_tech_tabelas.xlsx
+++ b/docs/descomplica_combo_tech_tabelas.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\descomplica_2026-2027\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\edyjrdev\descomplica_lab\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E8C66C7-887E-45BC-8A4B-E1455B315811}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FE6C2D8-3186-4E32-B5DF-06214C399255}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{FF1552BF-A68A-41CA-98A9-439A2B69C121}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FF1552BF-A68A-41CA-98A9-439A2B69C121}"/>
   </bookViews>
   <sheets>
     <sheet name="lista" sheetId="1" r:id="rId1"/>
@@ -1195,11 +1195,11 @@
       <c r="A2" s="2">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>0</v>
+      <c r="B2" s="5" t="s">
+        <v>8</v>
       </c>
       <c r="C2" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>163</v>
@@ -1210,14 +1210,14 @@
         <f>A2+1</f>
         <v>2</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>1</v>
+      <c r="B3" s="3" t="s">
+        <v>0</v>
       </c>
       <c r="C3" s="2">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="19.5" x14ac:dyDescent="0.25">
@@ -1226,13 +1226,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4" s="2">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="19.5" x14ac:dyDescent="0.25">
@@ -1241,10 +1241,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C5" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>163</v>
@@ -1256,13 +1256,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C6" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="19.5" x14ac:dyDescent="0.25">
@@ -1270,11 +1270,11 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>5</v>
+      <c r="B7" s="6" t="s">
+        <v>11</v>
       </c>
       <c r="C7" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>164</v>
@@ -1301,13 +1301,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C9" s="2">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="19.5" x14ac:dyDescent="0.25">
@@ -1316,13 +1316,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C10" s="2">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="19.5" x14ac:dyDescent="0.25">
@@ -1331,13 +1331,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C11" s="2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="19.5" x14ac:dyDescent="0.25">
@@ -1346,10 +1346,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C12" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>165</v>
@@ -1360,18 +1360,22 @@
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="B13" s="6" t="s">
-        <v>11</v>
+      <c r="B13" s="5" t="s">
+        <v>10</v>
       </c>
       <c r="C13" s="2">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:D13">
+    <sortCondition ref="C2:C13"/>
+  </sortState>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/docs/descomplica_combo_tech_tabelas.xlsx
+++ b/docs/descomplica_combo_tech_tabelas.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\edyjrdev\descomplica_lab\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FE6C2D8-3186-4E32-B5DF-06214C399255}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7CEC93E-6966-45C6-AAC0-8D8F0480D2DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FF1552BF-A68A-41CA-98A9-439A2B69C121}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{FF1552BF-A68A-41CA-98A9-439A2B69C121}"/>
   </bookViews>
   <sheets>
     <sheet name="lista" sheetId="1" r:id="rId1"/>
@@ -1381,6 +1381,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{024E7B97-303F-480E-A92A-F11B8F483FE2}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:D233"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1599,7 +1600,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="16" t="s">
         <v>8</v>
       </c>
@@ -1614,7 +1615,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="16" t="s">
         <v>8</v>
       </c>
@@ -1629,7 +1630,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="16" t="s">
         <v>8</v>
       </c>
@@ -1914,7 +1915,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="36" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="19" t="s">
         <v>0</v>
       </c>
@@ -1929,7 +1930,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="19" t="s">
         <v>0</v>
       </c>
@@ -1944,7 +1945,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="19" t="s">
         <v>0</v>
       </c>
@@ -2229,7 +2230,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="57" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" s="19" t="s">
         <v>1</v>
       </c>
@@ -2244,7 +2245,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="58" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" s="19" t="s">
         <v>1</v>
       </c>
@@ -2259,7 +2260,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="59" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:4" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" s="19" t="s">
         <v>1</v>
       </c>
@@ -2544,7 +2545,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="78" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:4" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" s="19" t="s">
         <v>2</v>
       </c>
@@ -2559,7 +2560,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="79" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:4" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" s="19" t="s">
         <v>2</v>
       </c>
@@ -2574,7 +2575,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="80" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:4" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" s="19" t="s">
         <v>2</v>
       </c>
@@ -2859,7 +2860,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="99" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:4" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" s="19" t="s">
         <v>3</v>
       </c>
@@ -2874,7 +2875,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="100" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:4" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" s="19" t="s">
         <v>3</v>
       </c>
@@ -2889,7 +2890,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="101" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:4" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" s="19" t="s">
         <v>3</v>
       </c>
@@ -3159,7 +3160,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="119" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:4" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119" s="19" t="s">
         <v>4</v>
       </c>
@@ -3174,7 +3175,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="120" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:4" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" s="19" t="s">
         <v>4</v>
       </c>
@@ -3189,7 +3190,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="121" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:4" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" s="19" t="s">
         <v>4</v>
       </c>
@@ -3459,7 +3460,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="139" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:4" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139" s="19" t="s">
         <v>5</v>
       </c>
@@ -3474,7 +3475,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="140" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:4" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140" s="19" t="s">
         <v>5</v>
       </c>
@@ -3489,7 +3490,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="141" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:4" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" s="19" t="s">
         <v>5</v>
       </c>
@@ -3774,7 +3775,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="160" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:4" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A160" s="19" t="s">
         <v>6</v>
       </c>
@@ -3789,7 +3790,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="161" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:4" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A161" s="19" t="s">
         <v>6</v>
       </c>
@@ -3804,7 +3805,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="162" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:4" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A162" s="19" t="s">
         <v>6</v>
       </c>
@@ -3999,7 +4000,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="175" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:4" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A175" s="20" t="s">
         <v>7</v>
       </c>
@@ -4014,7 +4015,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="176" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:4" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A176" s="20" t="s">
         <v>7</v>
       </c>
@@ -4029,7 +4030,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="177" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:4" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A177" s="20" t="s">
         <v>7</v>
       </c>
@@ -4239,7 +4240,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="191" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:4" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A191" s="19" t="s">
         <v>9</v>
       </c>
@@ -4254,7 +4255,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="192" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:4" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A192" s="19" t="s">
         <v>9</v>
       </c>
@@ -4269,7 +4270,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="193" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:4" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A193" s="19" t="s">
         <v>9</v>
       </c>
@@ -4539,7 +4540,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="211" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:4" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A211" s="19" t="s">
         <v>10</v>
       </c>
@@ -4554,7 +4555,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="212" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:4" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A212" s="19" t="s">
         <v>10</v>
       </c>
@@ -4569,7 +4570,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="213" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:4" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A213" s="19" t="s">
         <v>10</v>
       </c>
@@ -4839,7 +4840,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="231" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:4" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A231" s="20" t="s">
         <v>11</v>
       </c>
@@ -4854,7 +4855,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="232" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:4" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A232" s="20" t="s">
         <v>11</v>
       </c>
@@ -4869,7 +4870,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="233" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:4" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A233" s="20" t="s">
         <v>11</v>
       </c>
@@ -4885,7 +4886,17 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D233" xr:uid="{024E7B97-303F-480E-A92A-F11B8F483FE2}"/>
+  <autoFilter ref="A1:D233" xr:uid="{024E7B97-303F-480E-A92A-F11B8F483FE2}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="Conteúdo Bônus"/>
+        <filter val="Módulo 0"/>
+        <filter val="Módulo 1"/>
+        <filter val="Módulo 2"/>
+        <filter val="Módulo 3"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <hyperlinks>
     <hyperlink ref="C2" r:id="rId1" display="https://aulas.descomplica.com.br/pos/pos-graduacao-em-analise-de-dados-2a94b5/turma/estatistica-aplicada-a-negocios-b4022e" xr:uid="{00C33153-5E49-49D0-AC4D-CA8ED4C83DDF}"/>
     <hyperlink ref="C3" r:id="rId2" display="https://aulas.descomplica.com.br/pos/pos-graduacao-em-analise-de-dados-2a94b5/turma/computacao-e-inteligencia-artificial-efffc1" xr:uid="{DED76B29-3D1D-425F-B8BA-EE74156DFCCE}"/>
